--- a/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_67705_completo.xlsx
+++ b/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_67705_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfdb5933cc1d141f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1d9a61d6009c43f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,111 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -294,13 +399,298 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      7.1584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      7.0191</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/08/2026</x:t>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -315,22 +705,37 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.8811</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -345,97 +750,37 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.3423</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.2108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.3423</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.2108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -450,246 +795,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.8811</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.7445</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.7445</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6091</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6091</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6091</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.8811</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.0191</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.0191</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.2990</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.7445</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.8126</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6091</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.7445</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>16/07/2026</x:t>
         </x:is>
       </x:c>
@@ -699,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7445</x:v>
+        <x:v>      0.0632</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_67705_completo.xlsx
+++ b/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_67705_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1d9a61d6009c43f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb42df61b8f384318"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3397</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7285</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7285</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -280,6 +1000,36 @@
       </x:c>
       <x:c s="3">
         <x:v>      8.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7763</x:v>
       </x:c>
     </x:row>
     <x:row>
